--- a/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249928224896993</v>
+        <v>1.264320646241251</v>
       </c>
       <c r="C3" t="n">
-        <v>4.620641603239875</v>
+        <v>4.666803380293559</v>
       </c>
       <c r="D3" t="n">
-        <v>6.080243424430847</v>
+        <v>6.103952631488408</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95081325256771</v>
+        <v>12.03507665802322</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.364684520840705</v>
+        <v>1.401947023930771</v>
       </c>
       <c r="C4" t="n">
-        <v>5.124608395344653</v>
+        <v>5.235568372790466</v>
       </c>
       <c r="D4" t="n">
-        <v>6.444158578791319</v>
+        <v>6.314821435382057</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93345149497668</v>
+        <v>12.95233683210329</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.519807284177739</v>
+        <v>1.576080548031555</v>
       </c>
       <c r="C5" t="n">
-        <v>5.801135129223528</v>
+        <v>5.969372812504836</v>
       </c>
       <c r="D5" t="n">
-        <v>6.732462609868194</v>
+        <v>6.572404039643216</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05340502326946</v>
+        <v>14.11785740017961</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.695493756552039</v>
+        <v>1.769443903650414</v>
       </c>
       <c r="C6" t="n">
-        <v>6.644829872756532</v>
+        <v>6.870127725070671</v>
       </c>
       <c r="D6" t="n">
-        <v>7.142370587119153</v>
+        <v>6.822331880515361</v>
       </c>
       <c r="E6" t="n">
-        <v>15.48269421642772</v>
+        <v>15.46190350923645</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.891360645996615</v>
+        <v>1.985565954352653</v>
       </c>
       <c r="C7" t="n">
-        <v>7.690545717630855</v>
+        <v>7.910970669677472</v>
       </c>
       <c r="D7" t="n">
-        <v>7.605571365305928</v>
+        <v>7.130669481216124</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1874777289334</v>
+        <v>17.02720610524625</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.116521816304076</v>
+        <v>1.187432723594309</v>
       </c>
       <c r="C8" t="n">
-        <v>5.418875950039886</v>
+        <v>5.555096423473228</v>
       </c>
       <c r="D8" t="n">
-        <v>5.898483654727998</v>
+        <v>5.401551963402192</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43388142107196</v>
+        <v>12.14408111046973</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.372799993186837</v>
+        <v>1.459013020959476</v>
       </c>
       <c r="C9" t="n">
-        <v>6.731729269401428</v>
+        <v>6.868092445615577</v>
       </c>
       <c r="D9" t="n">
-        <v>6.457440069113941</v>
+        <v>5.897509496132338</v>
       </c>
       <c r="E9" t="n">
-        <v>14.56196933170221</v>
+        <v>14.22461496270739</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.630176893474301</v>
+        <v>1.746922105134437</v>
       </c>
       <c r="C10" t="n">
-        <v>8.190916141491286</v>
+        <v>8.349641754010539</v>
       </c>
       <c r="D10" t="n">
-        <v>6.994417566041555</v>
+        <v>6.377564605715678</v>
       </c>
       <c r="E10" t="n">
-        <v>16.81551060100714</v>
+        <v>16.47412846486066</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.887062917466961</v>
+        <v>2.031796897797308</v>
       </c>
       <c r="C11" t="n">
-        <v>9.786118901843327</v>
+        <v>9.908138816106582</v>
       </c>
       <c r="D11" t="n">
-        <v>7.508226295241795</v>
+        <v>6.826849034879579</v>
       </c>
       <c r="E11" t="n">
-        <v>19.18140811455208</v>
+        <v>18.76678474878347</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.139141005913336</v>
+        <v>2.322078611736238</v>
       </c>
       <c r="C12" t="n">
-        <v>11.43717631459656</v>
+        <v>11.48614437594942</v>
       </c>
       <c r="D12" t="n">
-        <v>8.02289503596894</v>
+        <v>7.25862757284565</v>
       </c>
       <c r="E12" t="n">
-        <v>21.59921235647883</v>
+        <v>21.06685056053131</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.371663274701235</v>
+        <v>2.602678700200654</v>
       </c>
       <c r="C13" t="n">
-        <v>13.10974937040538</v>
+        <v>13.12531962037098</v>
       </c>
       <c r="D13" t="n">
-        <v>8.529056358708168</v>
+        <v>7.621833589207112</v>
       </c>
       <c r="E13" t="n">
-        <v>24.01046900381478</v>
+        <v>23.34983190977875</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.375016199613998</v>
+        <v>1.51894041305658</v>
       </c>
       <c r="C14" t="n">
-        <v>9.130283101926462</v>
+        <v>9.16527259010582</v>
       </c>
       <c r="D14" t="n">
-        <v>6.450092234378586</v>
+        <v>5.809334960247821</v>
       </c>
       <c r="E14" t="n">
-        <v>16.95539153591904</v>
+        <v>16.49354796341022</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.371972781730833</v>
+        <v>1.536228990128367</v>
       </c>
       <c r="C15" t="n">
-        <v>9.864404582731101</v>
+        <v>9.825802263000117</v>
       </c>
       <c r="D15" t="n">
-        <v>6.476648509778463</v>
+        <v>5.781649674988061</v>
       </c>
       <c r="E15" t="n">
-        <v>17.7130258742404</v>
+        <v>17.14368092811655</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.559653490351695</v>
+        <v>1.768608671723586</v>
       </c>
       <c r="C16" t="n">
-        <v>11.67507132610462</v>
+        <v>11.58328773323459</v>
       </c>
       <c r="D16" t="n">
-        <v>6.915293384035937</v>
+        <v>6.179836726353525</v>
       </c>
       <c r="E16" t="n">
-        <v>20.15001820049226</v>
+        <v>19.5317331313117</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.228117290627548</v>
+        <v>1.404203558861255</v>
       </c>
       <c r="C17" t="n">
-        <v>10.77078351572288</v>
+        <v>10.6291467744312</v>
       </c>
       <c r="D17" t="n">
-        <v>6.411676446711409</v>
+        <v>5.687882951755449</v>
       </c>
       <c r="E17" t="n">
-        <v>18.41057725306184</v>
+        <v>17.7212332850479</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.377892720387441</v>
+        <v>1.589567342900096</v>
       </c>
       <c r="C18" t="n">
-        <v>12.59651026887955</v>
+        <v>12.40759255815134</v>
       </c>
       <c r="D18" t="n">
-        <v>6.823431251349564</v>
+        <v>6.059837704463438</v>
       </c>
       <c r="E18" t="n">
-        <v>20.79783424061656</v>
+        <v>20.05699760551487</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.364580221517854</v>
+        <v>1.58301908571277</v>
       </c>
       <c r="C19" t="n">
-        <v>13.50825936181356</v>
+        <v>13.27577168797088</v>
       </c>
       <c r="D19" t="n">
-        <v>6.905770431304743</v>
+        <v>6.125300641382615</v>
       </c>
       <c r="E19" t="n">
-        <v>21.77861001463616</v>
+        <v>20.98409141506626</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.505755541388546</v>
+        <v>1.751486991761522</v>
       </c>
       <c r="C20" t="n">
-        <v>15.55213045485387</v>
+        <v>15.27300976505946</v>
       </c>
       <c r="D20" t="n">
-        <v>7.326694759500564</v>
+        <v>6.459840989081758</v>
       </c>
       <c r="E20" t="n">
-        <v>24.38458075574298</v>
+        <v>23.48433774590274</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.891701804813293</v>
+        <v>1.038374911827767</v>
       </c>
       <c r="C21" t="n">
-        <v>11.45250912155187</v>
+        <v>11.25251729671975</v>
       </c>
       <c r="D21" t="n">
-        <v>6.096378354015504</v>
+        <v>5.351339838739642</v>
       </c>
       <c r="E21" t="n">
-        <v>18.44058928038067</v>
+        <v>17.64223204728716</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264320646241251</v>
+        <v>1.258449794969855</v>
       </c>
       <c r="C3" t="n">
-        <v>4.666803380293559</v>
+        <v>4.596451339807233</v>
       </c>
       <c r="D3" t="n">
-        <v>6.103952631488408</v>
+        <v>6.068354459732418</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03507665802322</v>
+        <v>11.92325559450951</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.401947023930771</v>
+        <v>1.386778583670285</v>
       </c>
       <c r="C4" t="n">
-        <v>5.235568372790466</v>
+        <v>5.020067259958169</v>
       </c>
       <c r="D4" t="n">
-        <v>6.314821435382057</v>
+        <v>6.306076321775361</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95233683210329</v>
+        <v>12.71292216540381</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.576080548031555</v>
+        <v>1.556493583380162</v>
       </c>
       <c r="C5" t="n">
-        <v>5.969372812504836</v>
+        <v>5.581773210162937</v>
       </c>
       <c r="D5" t="n">
-        <v>6.572404039643216</v>
+        <v>6.605414816696135</v>
       </c>
       <c r="E5" t="n">
-        <v>14.11785740017961</v>
+        <v>13.74368161023923</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.769443903650414</v>
+        <v>1.753764889775794</v>
       </c>
       <c r="C6" t="n">
-        <v>6.870127725070671</v>
+        <v>6.274915567147866</v>
       </c>
       <c r="D6" t="n">
-        <v>6.822331880515361</v>
+        <v>6.899531497646381</v>
       </c>
       <c r="E6" t="n">
-        <v>15.46190350923645</v>
+        <v>14.92821195457004</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.985565954352653</v>
+        <v>1.975818052613026</v>
       </c>
       <c r="C7" t="n">
-        <v>7.910970669677472</v>
+        <v>7.086113215637708</v>
       </c>
       <c r="D7" t="n">
-        <v>7.130669481216124</v>
+        <v>7.244168296577659</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02720610524625</v>
+        <v>16.30609956482839</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.187432723594309</v>
+        <v>1.203327924666858</v>
       </c>
       <c r="C8" t="n">
-        <v>5.555096423473228</v>
+        <v>4.718517748727364</v>
       </c>
       <c r="D8" t="n">
-        <v>5.401551963402192</v>
+        <v>5.407728795180974</v>
       </c>
       <c r="E8" t="n">
-        <v>12.14408111046973</v>
+        <v>11.3295744685752</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.459013020959476</v>
+        <v>1.513952832471953</v>
       </c>
       <c r="C9" t="n">
-        <v>6.868092445615577</v>
+        <v>5.674245719137776</v>
       </c>
       <c r="D9" t="n">
-        <v>5.897509496132338</v>
+        <v>5.836693549929747</v>
       </c>
       <c r="E9" t="n">
-        <v>14.22461496270739</v>
+        <v>13.02489210153947</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.746922105134437</v>
+        <v>1.846003685277087</v>
       </c>
       <c r="C10" t="n">
-        <v>8.349641754010539</v>
+        <v>6.728482007058946</v>
       </c>
       <c r="D10" t="n">
-        <v>6.377564605715678</v>
+        <v>6.31906221032049</v>
       </c>
       <c r="E10" t="n">
-        <v>16.47412846486066</v>
+        <v>14.89354790265652</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.031796897797308</v>
+        <v>2.189735433001071</v>
       </c>
       <c r="C11" t="n">
-        <v>9.908138816106582</v>
+        <v>7.873486465301719</v>
       </c>
       <c r="D11" t="n">
-        <v>6.826849034879579</v>
+        <v>6.789511349043472</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76678474878347</v>
+        <v>16.85273324734626</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.322078611736238</v>
+        <v>2.552346404785868</v>
       </c>
       <c r="C12" t="n">
-        <v>11.48614437594942</v>
+        <v>9.09816287593461</v>
       </c>
       <c r="D12" t="n">
-        <v>7.25862757284565</v>
+        <v>7.227016319194648</v>
       </c>
       <c r="E12" t="n">
-        <v>21.06685056053131</v>
+        <v>18.87752559991513</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.602678700200654</v>
+        <v>2.917701395283464</v>
       </c>
       <c r="C13" t="n">
-        <v>13.12531962037098</v>
+        <v>10.35692467564894</v>
       </c>
       <c r="D13" t="n">
-        <v>7.621833589207112</v>
+        <v>7.645443524380259</v>
       </c>
       <c r="E13" t="n">
-        <v>23.34983190977875</v>
+        <v>20.92006959531266</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.51894041305658</v>
+        <v>1.703283179483003</v>
       </c>
       <c r="C14" t="n">
-        <v>9.16527259010582</v>
+        <v>7.371158113025902</v>
       </c>
       <c r="D14" t="n">
-        <v>5.809334960247821</v>
+        <v>5.83649991922433</v>
       </c>
       <c r="E14" t="n">
-        <v>16.49354796341022</v>
+        <v>14.91094121173323</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.536228990128367</v>
+        <v>1.766389921911989</v>
       </c>
       <c r="C15" t="n">
-        <v>9.825802263000117</v>
+        <v>7.770523261636463</v>
       </c>
       <c r="D15" t="n">
-        <v>5.781649674988061</v>
+        <v>5.825631972138318</v>
       </c>
       <c r="E15" t="n">
-        <v>17.14368092811655</v>
+        <v>15.36254515568677</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.768608671723586</v>
+        <v>2.086164784139259</v>
       </c>
       <c r="C16" t="n">
-        <v>11.58328773323459</v>
+        <v>9.071329152286443</v>
       </c>
       <c r="D16" t="n">
-        <v>6.179836726353525</v>
+        <v>6.314974297843098</v>
       </c>
       <c r="E16" t="n">
-        <v>19.5317331313117</v>
+        <v>17.4724682342688</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.404203558861255</v>
+        <v>1.69216979547093</v>
       </c>
       <c r="C17" t="n">
-        <v>10.6291467744312</v>
+        <v>8.274267826162543</v>
       </c>
       <c r="D17" t="n">
-        <v>5.687882951755449</v>
+        <v>5.871371597679178</v>
       </c>
       <c r="E17" t="n">
-        <v>17.7212332850479</v>
+        <v>15.83780921931265</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.589567342900096</v>
+        <v>1.976209041263617</v>
       </c>
       <c r="C18" t="n">
-        <v>12.40759255815134</v>
+        <v>9.620214476253793</v>
       </c>
       <c r="D18" t="n">
-        <v>6.059837704463438</v>
+        <v>6.316338927152002</v>
       </c>
       <c r="E18" t="n">
-        <v>20.05699760551487</v>
+        <v>17.91276244466941</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.58301908571277</v>
+        <v>2.027927510323339</v>
       </c>
       <c r="C19" t="n">
-        <v>13.27577168797088</v>
+        <v>10.28020418791075</v>
       </c>
       <c r="D19" t="n">
-        <v>6.125300641382615</v>
+        <v>6.439018120274683</v>
       </c>
       <c r="E19" t="n">
-        <v>20.98409141506626</v>
+        <v>18.74714981850877</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.751486991761522</v>
+        <v>2.315245793448211</v>
       </c>
       <c r="C20" t="n">
-        <v>15.27300976505946</v>
+        <v>11.88060020798869</v>
       </c>
       <c r="D20" t="n">
-        <v>6.459840989081758</v>
+        <v>6.862622619703096</v>
       </c>
       <c r="E20" t="n">
-        <v>23.48433774590274</v>
+        <v>21.05846862114</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.038374911827767</v>
+        <v>1.415189315671777</v>
       </c>
       <c r="C21" t="n">
-        <v>11.25251729671975</v>
+        <v>8.848393883606079</v>
       </c>
       <c r="D21" t="n">
-        <v>5.351339838739642</v>
+        <v>5.708637098223226</v>
       </c>
       <c r="E21" t="n">
-        <v>17.64223204728716</v>
+        <v>15.97222029750108</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_68_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.258449794969855</v>
+        <v>2.596967636542405</v>
       </c>
       <c r="C3" t="n">
-        <v>4.596451339807233</v>
+        <v>7.682123867702584</v>
       </c>
       <c r="D3" t="n">
-        <v>6.068354459732418</v>
+        <v>8.316304067915812</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92325559450951</v>
+        <v>18.5953955721608</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.386778583670285</v>
+        <v>1.082209273881656</v>
       </c>
       <c r="C4" t="n">
-        <v>5.020067259958169</v>
+        <v>4.427559573002585</v>
       </c>
       <c r="D4" t="n">
-        <v>6.306076321775361</v>
+        <v>5.975190718042092</v>
       </c>
       <c r="E4" t="n">
-        <v>12.71292216540381</v>
+        <v>11.48495956492633</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.556493583380162</v>
+        <v>1.182367085422431</v>
       </c>
       <c r="C5" t="n">
-        <v>5.581773210162937</v>
+        <v>5.020878281714995</v>
       </c>
       <c r="D5" t="n">
-        <v>6.605414816696135</v>
+        <v>6.304791751985026</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74368161023923</v>
+        <v>12.50803711912245</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.753764889775794</v>
+        <v>1.287887875014084</v>
       </c>
       <c r="C6" t="n">
-        <v>6.274915567147866</v>
+        <v>5.769536688344228</v>
       </c>
       <c r="D6" t="n">
-        <v>6.899531497646381</v>
+        <v>6.747270834305108</v>
       </c>
       <c r="E6" t="n">
-        <v>14.92821195457004</v>
+        <v>13.80469539766342</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.975818052613026</v>
+        <v>1.391969823104629</v>
       </c>
       <c r="C7" t="n">
-        <v>7.086113215637708</v>
+        <v>6.663651724129354</v>
       </c>
       <c r="D7" t="n">
-        <v>7.244168296577659</v>
+        <v>7.171658468097712</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30609956482839</v>
+        <v>15.22728001533169</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.203327924666858</v>
+        <v>1.502045294312578</v>
       </c>
       <c r="C8" t="n">
-        <v>4.718517748727364</v>
+        <v>7.714973662408866</v>
       </c>
       <c r="D8" t="n">
-        <v>5.407728795180974</v>
+        <v>7.723863437434393</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3295744685752</v>
+        <v>16.94088239415584</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.513952832471953</v>
+        <v>1.596280931080472</v>
       </c>
       <c r="C9" t="n">
-        <v>5.674245719137776</v>
+        <v>8.888074588942905</v>
       </c>
       <c r="D9" t="n">
-        <v>5.836693549929747</v>
+        <v>8.194035006945676</v>
       </c>
       <c r="E9" t="n">
-        <v>13.02489210153947</v>
+        <v>18.67839052696905</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.846003685277087</v>
+        <v>1.005780888046772</v>
       </c>
       <c r="C10" t="n">
-        <v>6.728482007058946</v>
+        <v>6.610617801499982</v>
       </c>
       <c r="D10" t="n">
-        <v>6.31906221032049</v>
+        <v>6.457101912986909</v>
       </c>
       <c r="E10" t="n">
-        <v>14.89354790265652</v>
+        <v>14.07350060253366</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.189735433001071</v>
+        <v>0.9215862049305659</v>
       </c>
       <c r="C11" t="n">
-        <v>7.873486465301719</v>
+        <v>7.000891966369219</v>
       </c>
       <c r="D11" t="n">
-        <v>6.789511349043472</v>
+        <v>6.397352747706448</v>
       </c>
       <c r="E11" t="n">
-        <v>16.85273324734626</v>
+        <v>14.31983091900623</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.552346404785868</v>
+        <v>0.9807266866343938</v>
       </c>
       <c r="C12" t="n">
-        <v>9.09816287593461</v>
+        <v>8.276300043910334</v>
       </c>
       <c r="D12" t="n">
-        <v>7.227016319194648</v>
+        <v>6.893488767524617</v>
       </c>
       <c r="E12" t="n">
-        <v>18.87752559991513</v>
+        <v>16.15051549806935</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.917701395283464</v>
+        <v>0.765969376330404</v>
       </c>
       <c r="C13" t="n">
-        <v>10.35692467564894</v>
+        <v>7.900064871211828</v>
       </c>
       <c r="D13" t="n">
-        <v>7.645443524380259</v>
+        <v>6.375597218580339</v>
       </c>
       <c r="E13" t="n">
-        <v>20.92006959531266</v>
+        <v>15.04163146612257</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.703283179483003</v>
+        <v>0.8231365451486957</v>
       </c>
       <c r="C14" t="n">
-        <v>7.371158113025902</v>
+        <v>9.242487047044833</v>
       </c>
       <c r="D14" t="n">
-        <v>5.83649991922433</v>
+        <v>6.801351745481052</v>
       </c>
       <c r="E14" t="n">
-        <v>14.91094121173323</v>
+        <v>16.86697533767458</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.766389921911989</v>
+        <v>0.7947149491107505</v>
       </c>
       <c r="C15" t="n">
-        <v>7.770523261636463</v>
+        <v>9.981232559536471</v>
       </c>
       <c r="D15" t="n">
-        <v>5.825631972138318</v>
+        <v>6.918464429120656</v>
       </c>
       <c r="E15" t="n">
-        <v>15.36254515568677</v>
+        <v>17.69441193776788</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.086164784139259</v>
+        <v>0.8654302362476483</v>
       </c>
       <c r="C16" t="n">
-        <v>9.071329152286443</v>
+        <v>11.62745656244865</v>
       </c>
       <c r="D16" t="n">
-        <v>6.314974297843098</v>
+        <v>7.372395115133252</v>
       </c>
       <c r="E16" t="n">
-        <v>17.4724682342688</v>
+        <v>19.86528191382955</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.69216979547093</v>
+        <v>0.5228395573736814</v>
       </c>
       <c r="C17" t="n">
-        <v>8.274267826162543</v>
+        <v>8.701926943609497</v>
       </c>
       <c r="D17" t="n">
-        <v>5.871371597679178</v>
+        <v>6.155440295902991</v>
       </c>
       <c r="E17" t="n">
-        <v>15.83780921931265</v>
+        <v>15.38020679688617</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.976209041263617</v>
+        <v>0.4041953473154543</v>
       </c>
       <c r="C18" t="n">
-        <v>9.620214476253793</v>
+        <v>7.660007922569399</v>
       </c>
       <c r="D18" t="n">
-        <v>6.316338927152002</v>
+        <v>5.654709696828949</v>
       </c>
       <c r="E18" t="n">
-        <v>17.91276244466941</v>
+        <v>13.7189129667138</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.027927510323339</v>
+        <v>0.4723580904213104</v>
       </c>
       <c r="C19" t="n">
-        <v>10.28020418791075</v>
+        <v>9.487766893473855</v>
       </c>
       <c r="D19" t="n">
-        <v>6.439018120274683</v>
+        <v>6.274899356555744</v>
       </c>
       <c r="E19" t="n">
-        <v>18.74714981850877</v>
+        <v>16.23502434045091</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.315245793448211</v>
+        <v>0.5381253691288043</v>
       </c>
       <c r="C20" t="n">
-        <v>11.88060020798869</v>
+        <v>11.42482383629211</v>
       </c>
       <c r="D20" t="n">
-        <v>6.862622619703096</v>
+        <v>6.863329478050154</v>
       </c>
       <c r="E20" t="n">
-        <v>21.05846862114</v>
+        <v>18.82627868347107</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.415189315671777</v>
+        <v>0.5969124216591033</v>
       </c>
       <c r="C21" t="n">
-        <v>8.848393883606079</v>
+        <v>13.41929338485472</v>
       </c>
       <c r="D21" t="n">
-        <v>5.708637098223226</v>
+        <v>7.495447372383548</v>
       </c>
       <c r="E21" t="n">
-        <v>15.97222029750108</v>
+        <v>21.51165317889737</v>
       </c>
     </row>
   </sheetData>
